--- a/data/trans_camb/P19C04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 16,16</t>
+          <t>5,42; 15,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 7,99</t>
+          <t>-3,31; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 8,25</t>
+          <t>-1,96; 8,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 7,36</t>
+          <t>0,35; 7,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 3,38</t>
+          <t>-5,28; 3,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,26</t>
+          <t>-2,77; 4,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,17</t>
+          <t>3,57; 9,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,81</t>
+          <t>-2,84; 4,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,31</t>
+          <t>-1,28; 4,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 57,07</t>
+          <t>16,47; 54,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 28,62</t>
+          <t>-9,93; 27,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 29,29</t>
+          <t>-5,98; 29,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 36,09</t>
+          <t>1,04; 36,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 16,43</t>
+          <t>-22,09; 17,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 21,14</t>
+          <t>-11,5; 19,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 37,37</t>
+          <t>13,09; 40,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 15,36</t>
+          <t>-10,17; 15,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 17,55</t>
+          <t>-4,58; 19,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,41</t>
+          <t>-0,18; 5,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,64</t>
+          <t>-4,82; 0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -3,42</t>
+          <t>-10,19; -3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,62</t>
+          <t>-0,41; 4,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,34</t>
+          <t>-2,55; 2,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -1,52</t>
+          <t>-6,4; -1,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,49</t>
+          <t>0,64; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,93</t>
+          <t>-2,9; 0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; -2,91</t>
+          <t>-7,19; -2,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 32,83</t>
+          <t>-0,96; 33,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 3,93</t>
+          <t>-23,86; 5,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,85; -20,47</t>
+          <t>-52,95; -19,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 45,83</t>
+          <t>-3,13; 42,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 23,14</t>
+          <t>-19,83; 19,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -15,07</t>
+          <t>-50,96; -14,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 32,96</t>
+          <t>4,1; 33,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 6,87</t>
+          <t>-18,16; 5,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -20,73</t>
+          <t>-46,63; -21,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,06</t>
+          <t>-2,3; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,43</t>
+          <t>-3,21; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,3</t>
+          <t>-3,89; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,39</t>
+          <t>-2,06; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,99</t>
+          <t>-1,8; 4,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,09</t>
+          <t>-4,54; 1,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,74</t>
+          <t>-1,11; 4,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,18</t>
+          <t>-1,63; 3,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,24</t>
+          <t>-3,27; 1,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 93,38</t>
+          <t>-23,63; 92,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 70,41</t>
+          <t>-31,74; 66,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 50,15</t>
+          <t>-36,86; 49,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 119,12</t>
+          <t>-26,83; 112,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 112,81</t>
+          <t>-24,55; 106,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,21; 26,69</t>
+          <t>-52,65; 30,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 76,49</t>
+          <t>-12,67; 71,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 53,27</t>
+          <t>-18,76; 61,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 20,73</t>
+          <t>-37,27; 21,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,1</t>
+          <t>2,74; 7,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,06</t>
+          <t>-4,2; 0,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -3,05</t>
+          <t>-8,59; -3,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,86</t>
+          <t>0,87; 4,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,3</t>
+          <t>-3,34; 0,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -2,32</t>
+          <t>-6,46; -2,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,36</t>
+          <t>2,3; 5,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,31</t>
+          <t>-3,2; -0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -3,28</t>
+          <t>-6,82; -3,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 37,78</t>
+          <t>12,41; 37,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 0,38</t>
+          <t>-19,6; 0,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -16,24</t>
+          <t>-42,51; -16,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,84; 35,45</t>
+          <t>5,57; 34,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 2,18</t>
+          <t>-21,76; 3,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -17,33</t>
+          <t>-41,8; -17,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5; 32,72</t>
+          <t>12,65; 32,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,36; -1,82</t>
+          <t>-17,85; -0,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,64; -19,89</t>
+          <t>-38,02; -20,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,16</t>
+          <t>5,48; 15,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 7,97</t>
+          <t>-2,96; 8,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,37</t>
+          <t>-2,07; 8,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,74</t>
+          <t>-0,03; 7,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,64</t>
+          <t>-5,51; 3,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,17</t>
+          <t>-3,05; 4,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,83</t>
+          <t>3,8; 9,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,0</t>
+          <t>-2,76; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,75</t>
+          <t>-1,35; 4,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 54,84</t>
+          <t>16,26; 53,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 27,79</t>
+          <t>-9,08; 28,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 29,31</t>
+          <t>-6,3; 30,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 36,32</t>
+          <t>-0,51; 35,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 17,74</t>
+          <t>-23,01; 17,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 19,96</t>
+          <t>-12,45; 19,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09; 40,9</t>
+          <t>13,86; 39,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 15,94</t>
+          <t>-10,16; 16,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 19,51</t>
+          <t>-4,9; 17,97</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,18</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,81</t>
+          <t>-2,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,74</t>
+          <t>-0,25; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,84</t>
+          <t>-4,78; 0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -3,12</t>
+          <t>-6,27; -0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,44</t>
+          <t>-0,25; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,03</t>
+          <t>-2,54; 2,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; -1,54</t>
+          <t>-4,29; -0,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,61</t>
+          <t>0,55; 4,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,79</t>
+          <t>-2,78; 0,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -2,93</t>
+          <t>-4,56; -1,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,91%</t>
+          <t>-20,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-31,15%</t>
+          <t>-18,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-32,41%</t>
+          <t>-18,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 33,59</t>
+          <t>-1,26; 33,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 5,04</t>
+          <t>-24,37; 3,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,95; -19,25</t>
+          <t>-31,73; -4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 42,95</t>
+          <t>-2,07; 44,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 19,86</t>
+          <t>-20,18; 20,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,96; -14,74</t>
+          <t>-32,64; -1,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 33,02</t>
+          <t>3,62; 31,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 5,78</t>
+          <t>-17,59; 6,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,63; -21,43</t>
+          <t>-28,53; -8,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,9</t>
+          <t>-2,22; 6,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,99</t>
+          <t>-3,28; 4,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,11</t>
+          <t>-3,68; 3,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,14</t>
+          <t>-2,08; 5,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,86</t>
+          <t>-2,23; 5,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,25</t>
+          <t>-4,32; 0,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,41</t>
+          <t>-1,15; 4,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,64</t>
+          <t>-1,92; 3,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,19</t>
+          <t>-3,1; 1,61</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,96%</t>
+          <t>-1,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-22,93%</t>
+          <t>-22,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,03%</t>
+          <t>-11,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 92,66</t>
+          <t>-21,72; 97,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 66,43</t>
+          <t>-33,28; 66,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 49,9</t>
+          <t>-35,28; 56,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 112,14</t>
+          <t>-30,13; 115,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 106,46</t>
+          <t>-29,28; 114,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 30,06</t>
+          <t>-52,75; 22,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 71,61</t>
+          <t>-14,7; 77,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 61,4</t>
+          <t>-21,45; 52,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 21,91</t>
+          <t>-35,52; 29,76</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-3,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,1</t>
+          <t>2,58; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,02</t>
+          <t>-4,42; 0,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -3,17</t>
+          <t>-5,52; -1,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,75</t>
+          <t>0,89; 4,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,45</t>
+          <t>-3,6; 0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -2,36</t>
+          <t>-4,92; -1,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,41</t>
+          <t>2,31; 5,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,16</t>
+          <t>-3,27; -0,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -3,3</t>
+          <t>-4,58; -1,97</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-17,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,35%</t>
+          <t>-21,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-27,63%</t>
+          <t>-19,27%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,41; 37,28</t>
+          <t>12,29; 37,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 0,39</t>
+          <t>-21,26; 0,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,51; -16,97</t>
+          <t>-26,35; -8,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 34,86</t>
+          <t>5,92; 34,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 3,15</t>
+          <t>-22,97; 1,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -17,43</t>
+          <t>-31,1; -11,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,65; 32,76</t>
+          <t>12,81; 32,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -0,95</t>
+          <t>-18,15; -2,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -20,06</t>
+          <t>-25,49; -11,84</t>
         </is>
       </c>
     </row>
